--- a/Capitulo_3_1/CEI/CEI_COMPLETA.xlsx
+++ b/Capitulo_3_1/CEI/CEI_COMPLETA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af58cd692ca3cd0e/Documentos/Doutorado/Projeto de Tese/DADOS2023-09-30/ARTIGO/2024-07-15/Artigo_Endividamento_AKB/Cálculos/CEI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af58cd692ca3cd0e/Documentos/Doutorado/Projeto de Tese/TESE_Paim/Capitulo_3_1/CEI/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{A07D23E1-9B10-47F0-BEB2-433449F866BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81AD85EF-B7F1-4346-B7CA-55794A0D10F5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{29014B1F-C995-4932-9AD1-490E322FFCD5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29014B1F-C995-4932-9AD1-490E322FFCD5}"/>
   </bookViews>
   <sheets>
     <sheet name="CEI_COMPLETA" sheetId="2" r:id="rId1"/>
@@ -2160,6 +2160,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2167,7 +2168,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2969,6 +2969,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2976,7 +2977,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3979,6 +3979,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3986,7 +3987,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4937,6 +4937,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4944,7 +4945,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5876,6 +5876,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5883,7 +5884,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
